--- a/stories/arbres/ATOM-TMP.JOU.001-03.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le jour, Léa est au balcon avec maman. Le soleil brille. Il fait chaud. Maman dit : le jour, c'est le soleil. Le soir arrive. Le ciel devient bleu foncé. Léa voit la lune. Elle voit les étoiles. Maman dit : la nuit, c'est la lune. Léa met son pyjama. Maman dit : la nuit, on fait dodo. Léa se couche. Elle ferme les yeux. Dodo la nuit.</t>
+          <t>Le jour, Léa est au balcon avec maman. Le soleil brille. Il fait chaud. Le jour, c'est le soleil. Le soir arrive. Le ciel devient bleu foncé. Léa voit la lune. Elle voit les étoiles. La nuit, c'est la lune. Léa met son pyjama. La nuit, on fait dodo. Léa se couche. Elle ferme les yeux. Dodo la nuit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le jour, Léa est au balcon avec maman. Le soleil brille. Il fait chaud.
+maman|Le jour, c'est le soleil.
+narrateur|Le soir arrive. Le ciel devient bleu foncé. Léa voit la lune. Elle voit les étoiles.
+maman|La nuit, c'est la lune.
+narrateur|Léa met son pyjama.
+maman|La nuit, on fait dodo.
+narrateur|Léa se couche. Elle ferme les yeux. Dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La lune est là. Quel moment est-ce ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a vu le soleil le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1836,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman baisse la lumière. Léa respire.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2003,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.JOU.001-03.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Léa se couche. Elle ferme les yeux. Dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|La lune est là. Quel moment est-ce ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Léa a vu le soleil le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1849,7 @@
           <t>narrateur|Maman baisse la lumière. Léa respire.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.JOU.001-03.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Léa voit le soleil puis la lune</t>
+          <t>Les tomates d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss veut une tomate rouge pour la salade. Le soleil chauffe le fruit. L'arrosoir verse de travers. Le soir, la lune pose un rond blanc sur le même pied.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le jour, Léa est au balcon avec maman. Le soleil brille. Il fait chaud. Le jour, c'est le soleil. Le soir arrive. Le ciel devient bleu foncé. Léa voit la lune. Elle voit les étoiles. La nuit, c'est la lune. Léa met son pyjama. La nuit, on fait dodo. Léa se couche. Elle ferme les yeux. Dodo la nuit.</t>
+          <t>Les feuilles de tomate sentent le vert, fort. La terre du rang est sèche, déjà. Une abeille tourne autour d'une fleur jaune. Le tuteur en bois est chaud. Tu as senti les feuilles, Aniss ? Ça sent fort. Oui. C'est le pied de tomate. Je veux une tomate rouge. Pour la salade, ce soir ? Oui. En ce moment, Aniss touche un fruit. Le soleil le rend lisse et chaud. Un autre fruit est encore vert, dur. Le jour chauffe les rouges. Le soleil est sur les tomates. Aniss lève l'arrosoir. L'eau part de travers, trop vite. La terre fait une flaque, puis boit. Oh. Ça a trop coulé. On verse plus lentement ? Oui. Aniss penche l'arrosoir tout doux. L'eau file au pied, sans flaque. Merci, Aniss. Tu as rattrapé l'eau. Il cherche la plus rouge. Celle-là est trop haute, un peu. Je te la tends. La tomate se détache, tiède. Elle est chaude. Le soleil l'a tenue. Ils la posent dans le panier. Le panier sent l'osier sec. Plus tard, l'air refroidit les feuilles. Le ciel passe au bleu foncé. Une lune ronde s'accroche au tuteur. Elle est sur le pied. La nuit est là. La lune est sur les tomates.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le jour, Léa est au balcon avec maman. Le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt; brille. Il fait chaud. Maman dit : le jour, c'est le soleil. Le soir arrive. Le ciel devient bleu foncé. Léa voit la lune. Elle voit les étoiles. Maman dit : la nuit, c'est la lune. Léa met son pyjama. Maman dit : la nuit, on fait dodo. Léa se couche. Elle ferme les yeux. Dodo la nuit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les feuilles de tomate sentent le vert, fort. La terre du rang est sèche, déjà. Une abeille tourne autour d'une fleur jaune. Le tuteur en bois est chaud. Tu as senti les feuilles, Aniss ? Ça sent fort. Oui. C'est le pied de tomate. Je veux une tomate rouge. Pour la salade, ce soir ? Oui. En ce moment, Aniss touche un fruit. Le soleil le rend lisse et chaud. Un autre fruit est encore vert, dur. Le jour chauffe les rouges. Le soleil est sur les tomates. Aniss lève l'arrosoir. L'eau part de travers, trop vite. La terre fait une flaque, puis boit. Oh. Ça a trop coulé. On verse plus lentement ? Oui. Aniss penche l'arrosoir tout doux. L'eau file au pied, sans flaque. Merci, Aniss. Tu as rattrapé l'eau. Il cherche la plus rouge. Celle-là est trop haute, un peu. Je te la tends. La tomate se détache, tiède. Elle est chaude. Le soleil l'a tenue. Ils la posent dans le panier. Le panier sent l'osier sec. Plus tard, l'air refroidit les feuilles. Le ciel passe au bleu foncé. Une lune ronde s'accroche au tuteur. Elle est sur le pied. La nuit est là. La lune est sur les tomates.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,16 +1324,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le jour, Léa est au balcon avec maman. Le soleil brille. Il fait chaud.
-maman|Le jour, c'est le soleil.
-narrateur|Le soir arrive. Le ciel devient bleu foncé. Léa voit la lune. Elle voit les étoiles.
-maman|La nuit, c'est la lune.
-narrateur|Léa met son pyjama.
-maman|La nuit, on fait dodo.
-narrateur|Léa se couche. Elle ferme les yeux. Dodo la nuit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les feuilles de tomate sentent le vert, fort.
+narrateur|La terre du rang est sèche, déjà.
+narrateur|Une abeille tourne autour d'une fleur jaune.
+narrateur|Le tuteur en bois est chaud.
+maman|Tu as senti les feuilles, Aniss ?
+enfant-m|Ça sent fort.
+maman|Oui.
+maman|C'est le pied de tomate.
+enfant-m|Je veux une tomate rouge.
+maman|Pour la salade, ce soir ?
+enfant-m|Oui.
+narrateur|En ce moment, Aniss touche un fruit.
+narrateur|Le soleil le rend lisse et chaud.
+narrateur|Un autre fruit est encore vert, dur.
+maman|Le jour chauffe les rouges.
+maman|Le soleil est sur les tomates.
+narrateur|Aniss lève l'arrosoir.
+narrateur|L'eau part de travers, trop vite.
+narrateur|La terre fait une flaque, puis boit.
+enfant-m|Oh.
+enfant-m|Ça a trop coulé.
+maman|On verse plus lentement ?
+enfant-m|Oui.
+narrateur|Aniss penche l'arrosoir tout doux.
+narrateur|L'eau file au pied, sans flaque.
+maman|Merci, Aniss.
+maman|Tu as rattrapé l'eau.
+narrateur|Il cherche la plus rouge.
+narrateur|Celle-là est trop haute, un peu.
+maman|Je te la tends.
+narrateur|La tomate se détache, tiède.
+enfant-m|Elle est chaude.
+maman|Le soleil l'a tenue.
+narrateur|Ils la posent dans le panier.
+narrateur|Le panier sent l'osier sec.
+narrateur|Plus tard, l'air refroidit les feuilles.
+narrateur|Le ciel passe au bleu foncé.
+narrateur|Une lune ronde s'accroche au tuteur.
+enfant-m|Elle est sur le pied.
+maman|La nuit est là.
+maman|La lune est sur les tomates.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,12 +1396,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La lune est là. Quel moment est-ce ?</t>
+          <t>La lune est sur le pied. Quel moment est-ce ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;lune&lt;/emphasis&gt; est là. Quel moment est-ce ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La lune est sur le pied. Quel moment est-ce ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1366,7 +1416,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>nuit | la nuit | lune | le soir</t>
+          <t>nuit | la nuit | le soir | dodo | c'est la nuit</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1381,7 +1431,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>La lune vient la nuit. Quel moment ?</t>
+          <t>La lune est sur les tomates. C'est le jour, ou la nuit ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1430,7 +1480,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1556,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La lune est là. Quel moment est-ce ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La lune est sur le pied.
+narrateur|Quel moment est-ce ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1534,12 +1584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa a vu le soleil le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.</t>
+          <t>Aniss a cueilli au soleil, le fruit chaud. Maintenant la lune pose un rond sur les feuilles. Le jour, c'était le soleil. La nuit, c'est la lune. Le même pied. Oui. On rentre avec le panier ? La salade. Les tomates vertes restent dehors. Elles sont plus pâles, sous la lune. Elles attendront demain.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Léa a vu le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt; le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a cueilli au soleil, le fruit chaud. Maintenant la lune pose un rond sur les feuilles. Le jour, c'était le soleil. La nuit, c'est la lune. Le même pied. Oui. On rentre avec le panier ? La salade. Les tomates vertes restent dehors. Elles sont plus pâles, sous la lune. Elles attendront demain.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1602,7 +1652,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1678,10 +1728,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léa a vu le soleil le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss a cueilli au soleil, le fruit chaud.
+narrateur|Maintenant la lune pose un rond sur les feuilles.
+maman|Le jour, c'était le soleil.
+maman|La nuit, c'est la lune.
+enfant-m|Le même pied.
+maman|Oui.
+maman|On rentre avec le panier ?
+enfant-m|La salade.
+narrateur|Les tomates vertes restent dehors.
+narrateur|Elles sont plus pâles, sous la lune.
+maman|Elles attendront demain.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,12 +1765,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman baisse la lumière. Léa respire.</t>
+          <t>La cuisine sent la tomate coupée. Le fruit est encore tiède au couteau. Elle est sucrée. Le soleil l'avait gardée. La nuit, on se couche. Tu mets le pyjama ? Oui. Aniss enfile le pyjama, les doigts un peu verts. À la fenêtre, le pied est déjà sombre. La lune est encore là ? Sur les feuilles, oui. Maman baisse la lumière. Aniss respire le vert des tomates.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman bais&lt;emphasis level="moderate"&gt;se&lt;/emphasis&gt; la lumière. Léa respire.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La cuisine sent la tomate coupée. Le fruit est encore tiède au couteau. Elle est sucrée. Le soleil l'avait gardée. La nuit, on se couche. Tu mets le pyjama ? Oui. Aniss enfile le pyjama, les doigts un peu verts. À la fenêtre, le pied est déjà sombre. La lune est encore là ? Sur les feuilles, oui. Maman baisse la lumière. Aniss respire le vert des tomates.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1774,7 +1833,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1846,10 +1905,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman baisse la lumière. Léa respire.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La cuisine sent la tomate coupée.
+narrateur|Le fruit est encore tiède au couteau.
+enfant-m|Elle est sucrée.
+maman|Le soleil l'avait gardée.
+maman|La nuit, on se couche.
+maman|Tu mets le pyjama ?
+enfant-m|Oui.
+narrateur|Aniss enfile le pyjama, les doigts un peu verts.
+narrateur|À la fenêtre, le pied est déjà sombre.
+enfant-m|La lune est encore là ?
+maman|Sur les feuilles, oui.
+narrateur|Maman baisse la lumière.
+narrateur|Aniss respire le vert des tomates.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1874,12 +1944,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss pose le noyau dans le compost. À la fenêtre, le pied est noir. La lune tient encore une feuille. Elle est toujours là. Oui. Sur le même pied. Aniss ferme les yeux, le vert aux doigts.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss pose le noyau dans le compost. À la fenêtre, le pied est noir. La lune tient encore une feuille. Elle est toujours là. Oui. Sur le même pied. Aniss ferme les yeux, le vert aux doigts.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1935,14 +2005,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2014,10 +2084,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Aniss pose le noyau dans le compost.
+narrateur|À la fenêtre, le pied est noir.
+narrateur|La lune tient encore une feuille.
+enfant-m|Elle est toujours là.
+maman|Oui.
+maman|Sur le même pied.
+narrateur|Aniss ferme les yeux, le vert aux doigts.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2036,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2149,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.JOU.001-03.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>balcon</t>
+          <t>jardin, pied de tomate</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léa, maman</t>
+          <t>Aniss, maman</t>
         </is>
       </c>
     </row>
